--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/abr-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/abr-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/abr-2025.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/abr-2025.xlsx
@@ -684,7 +684,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +993,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1851,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +1977,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2042,11 @@
           <t>77.942.697-1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2107,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2355,11 @@
           <t>78.616.370-6</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2603,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2790,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3038,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3164,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3290,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3477,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3542,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3790,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3855,11 @@
           <t>77.909.208-9</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4042,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4290,11 @@
           <t>77.942.697-1</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4355,11 @@
           <t>76.102.347-0</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4603,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4790,11 @@
           <t>78.616.370-6</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5038,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5103,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5229,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5355,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5420,11 @@
           <t>76.359.833-0</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5546,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5672,11 @@
           <t>77.888.564-6</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5737,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5863,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +5928,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +5993,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6180,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6428,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6554,11 @@
           <t>76.102.347-0</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6741,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6806,11 @@
           <t>77.820.166-6</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7115,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7180,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7306,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7554,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7619,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7745,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7810,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +7936,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8001,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8066,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8192,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8257,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8383,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8631,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8696,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8761,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8887,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9013,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9078,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9326,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9391,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9456,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9643,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9830,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10017,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10082,11 @@
           <t>76.102.347-0</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10391,11 @@
           <t>77.721.515-9</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10639,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10765,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +10952,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11017,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11082,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11330,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11395,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11582,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11647,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11712,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11777,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +11842,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +11907,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12155,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12281,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12529,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12594,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12720,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +12785,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12850,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
